--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0C1E63-1E91-4A40-B3F1-AF634D5A559F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493D68D5-2701-44A4-9648-398EBFBA95EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7044" yWindow="2088" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000,1,500&amp;1001,1,500&amp;2000,1,500&amp;3000,1,500&amp;4000,1,500&amp;4001,1,500</t>
+    <t>1000,1,500&amp;1001,1,500&amp;2000,1,500&amp;3000,1,500&amp;4000,1,500&amp;4001,1,500&amp;101,1000,10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -104,6 +104,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493D68D5-2701-44A4-9648-398EBFBA95EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5612311-D212-4090-9022-26CAAE0C06AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7044" yWindow="2088" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000,1,500&amp;1001,1,500&amp;2000,1,500&amp;3000,1,500&amp;4000,1,500&amp;4001,1,500&amp;101,1000,10000</t>
+    <t>1000,1,500&amp;1001,1,500&amp;2000,1,500&amp;3000,1,500&amp;4000,1,500&amp;4001,1,500&amp;101,1000,500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -422,16 +422,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="51.875" customWidth="1"/>
+    <col min="5" max="5" width="82.875" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +449,7 @@
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -467,7 +467,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -485,7 +485,7 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -503,7 +503,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5612311-D212-4090-9022-26CAAE0C06AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CEDD7E-0A0B-4A16-8AB3-94A4214E29C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5988" yWindow="3768" windowWidth="21216" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000,1,500&amp;1001,1,500&amp;2000,1,500&amp;3000,1,500&amp;4000,1,500&amp;4001,1,500&amp;101,1000,500</t>
+    <t>1000,1,500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -422,16 +422,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="51.875" customWidth="1"/>
-    <col min="5" max="5" width="82.875" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" customWidth="1"/>
+    <col min="5" max="5" width="82.88671875" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +449,7 @@
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -467,7 +467,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -485,7 +485,7 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -503,7 +503,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CEDD7E-0A0B-4A16-8AB3-94A4214E29C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7D05DF-B6A9-46CD-A664-0E42C800151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5988" yWindow="3768" windowWidth="21216" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="384" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000,1,500</t>
+    <t>1001,1,500&amp;1001,1,500&amp;1002,2,500&amp;1003,1,500&amp;1004,1,500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7D05DF-B6A9-46CD-A664-0E42C800151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468AF0C1-2CA2-4A5D-BE43-B0DDB58822C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="384" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -81,11 +81,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>普通奖池，消耗时间币 * 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,1,500&amp;1001,1,500&amp;1002,2,500&amp;1003,1,500&amp;1004,1,500</t>
+    <t>神秘转盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘转盘，消耗转盘币 * 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useCoin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗的货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1,500&amp;1002,2,500&amp;1003,1,500&amp;1004,1,500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;,4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通奖池，消耗时间币 * 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>104,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -421,17 +457,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
-    <col min="5" max="5" width="82.88671875" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="51.875" customWidth="1"/>
+    <col min="5" max="5" width="82.875" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,9 +483,11 @@
       <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -465,9 +503,11 @@
       <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -483,9 +523,11 @@
       <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -501,9 +543,11 @@
       <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -511,10 +555,30 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468AF0C1-2CA2-4A5D-BE43-B0DDB58822C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FBB1ED-E9B0-45DC-B542-80DFCC0F1A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -105,10 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1,500&amp;1002,2,500&amp;1003,1,500&amp;1004,1,500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;,4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,6 +118,10 @@
   </si>
   <si>
     <t>104,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1,500&amp;1001,1,500&amp;1002,2,500&amp;1003,1,500&amp;1004,1,500&amp;3000,1,10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,16 +458,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="51.875" customWidth="1"/>
-    <col min="5" max="5" width="82.875" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" customWidth="1"/>
+    <col min="5" max="5" width="82.88671875" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,7 +487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -507,7 +507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -527,7 +527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -547,7 +547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -555,16 +555,16 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -575,10 +575,10 @@
         <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FBB1ED-E9B0-45DC-B542-80DFCC0F1A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5522AE25-D0EB-4868-9594-E4EBFA02293C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -121,7 +121,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1,500&amp;1001,1,500&amp;1002,2,500&amp;1003,1,500&amp;1004,1,500&amp;3000,1,10000</t>
+    <t>时光秘匣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时光秘匣，消耗秘匣币 * 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;,4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
+  </si>
+  <si>
+    <t>105,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1,500&amp;1001,1,500&amp;1002,2,500&amp;1003,1,500&amp;1004,1,500&amp;5003,1,10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -457,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.109375" customWidth="1"/>
@@ -558,7 +573,7 @@
         <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>23</v>
@@ -579,6 +594,23 @@
       </c>
       <c r="F6" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
